--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6804R_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6804R_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX3"/>
+  <dimension ref="A1:BX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,13 +833,13 @@
         <v>0.375</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.575</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3</v>
+        <v>0.2812</v>
       </c>
       <c r="O2" t="n">
-        <v>0.058</v>
+        <v>0.04</v>
       </c>
       <c r="P2" t="n">
         <v>0.38</v>
@@ -872,7 +872,7 @@
         <v>0.28125</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.367</v>
+        <v>0.349</v>
       </c>
       <c r="AA2" t="n">
         <v>0.75</v>
@@ -950,7 +950,7 @@
         <v>0.05556</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.367</v>
+        <v>0.349</v>
       </c>
       <c r="BA2" t="n">
         <v>0.03007</v>
@@ -986,7 +986,7 @@
         <v>0.539</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.575</v>
       </c>
       <c r="BM2" t="n">
         <v>0.75</v>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>forged (-FG): Air-Way non-forged FF6804-6-6-6 NWO = Brennan forged FS6804-06-06-06-NWO-FG p18 on every compared cell (M1 LGTH ~ L7 (1), N LGTH ~ L10, M2 LGTH ~ L7 (3), C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6804 is used only where Brennan FS6804-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5691 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.47 = L10 - L11 (Air-Way), thread 0.367 = stud - undercut 0.103, tip -&gt; body face 0.893 (FS lock nut 0.33 thick, NWO_FS)</t>
+          <t>forged (-FG): Air-Way non-forged FF6804-6-6-6 NWO = Brennan forged FS6804-06-06-06-NWO-FG p18 on every compared cell (M1 LGTH ~ L7 (1), N LGTH ~ L10, M2 LGTH ~ L7 (3), C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6804 is used only where Brennan FS6804-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5691 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.47 = L10 - L11 (Air-Way), thread 0.349 = stud - undercut 0.121, tip -&gt; body face 0.875 (FS lock nut 0.33 thick, NWO_FS)</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
@@ -1085,13 +1085,13 @@
         <v>0.375</v>
       </c>
       <c r="M3" t="n">
-        <v>0.537</v>
+        <v>0.555</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3</v>
+        <v>0.2812</v>
       </c>
       <c r="O3" t="n">
-        <v>0.058</v>
+        <v>0.04</v>
       </c>
       <c r="P3" t="n">
         <v>0.38</v>
@@ -1124,7 +1124,7 @@
         <v>0.28125</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.377</v>
+        <v>0.359</v>
       </c>
       <c r="AA3" t="n">
         <v>0.75</v>
@@ -1202,7 +1202,7 @@
         <v>0.05556</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.377</v>
+        <v>0.359</v>
       </c>
       <c r="BA3" t="n">
         <v>0.03007</v>
@@ -1238,7 +1238,7 @@
         <v>0.596</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.537</v>
+        <v>0.555</v>
       </c>
       <c r="BM3" t="n">
         <v>0.75</v>
@@ -1288,12 +1288,264 @@
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>forged (-FG): Air-Way non-forged FF6804-8-6-8 NWO = Brennan forged FS6804-08-06-08-NWO-FG p18 on every compared cell (M1 LGTH ~ L7 (1), N LGTH ~ L10, M2 LGTH ~ L7 (3), C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6804 is used only where Brennan FS6804-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5692 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.48 = L10 - L11 (Air-Way), thread 0.377 = stud - undercut 0.103, tip -&gt; body face 0.903 (FS lock nut 0.33 thick, NWO_FS)</t>
+          <t>forged (-FG): Air-Way non-forged FF6804-8-6-8 NWO = Brennan forged FS6804-08-06-08-NWO-FG p18 on every compared cell (M1 LGTH ~ L7 (1), N LGTH ~ L10, M2 LGTH ~ L7 (3), C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6804 is used only where Brennan FS6804-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5692 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.48 = L10 - L11 (Air-Way), thread 0.359 = stud - undercut 0.121, tip -&gt; body face 0.885 (FS lock nut 0.33 thick, NWO_FS)</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
           <t>FS6804-08-06-08-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FS6804-10-10-10-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="F4" t="n">
+        <v>45</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.62199</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5775</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>FS6804-10-10-10-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>ORFS Male Face Seal x Adjustable Male ORB Run Tee - stud neck below the flats, 1-14 UN (male O-ring face seal, SAE J1453) x 7/8-14 (adjustable male ORB) x 1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>FS6804R</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>7/8-14 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>Air-Way FF6804 (s38, double-pass 2026-10-15, parts.air-way.com/api/series/38, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p18 FS6804-10-10-10-NWO-FG (ORFS-p018-t01); FORGED part: Air-Way NON-forged row FF6804-10-10-10 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF6804-10-10-10 NWO = Brennan forged FS6804-10-10-10-NWO-FG p18 on every compared cell (M1 LGTH ~ L7 (1), N LGTH ~ L10, M2 LGTH ~ L7 (3), C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6804 is used only where Brennan FS6804-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5694 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.63 = L10 - L11 (Air-Way), thread 0.461 = stud - undercut 0.169, tip -&gt; body face 1.186 (FS lock nut 0.45 thick, NWO_FS)</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>FS6804-10-10-10-NWO-FG</t>
         </is>
       </c>
     </row>

--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6804R_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6804R_SW2.xlsx
@@ -1031,7 +1031,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>Air-Way FF6804 (s38, double-pass 2026-10-15, parts.air-way.com/api/series/38, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p18 FS6804-06-06-06-NWO-FG (ORFS-p018-t01); FORGED part: Air-Way NON-forged row FF6804-6-6-6 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6804 (s38, double-pass 2026-10-15, parts.air-way.com/api/series/38, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p18 FS6804-06-06-06-NWO-FG (ORFS-p018-t01); FORGED part: Air-Way NON-forged row FF6804-6-6-6 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>Air-Way FF6804 (s38, double-pass 2026-10-15, parts.air-way.com/api/series/38, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p18 FS6804-08-06-08-NWO-FG (ORFS-p018-t01); FORGED part: Air-Way NON-forged row FF6804-8-6-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6804 (s38, double-pass 2026-10-15, parts.air-way.com/api/series/38, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p18 FS6804-08-06-08-NWO-FG (ORFS-p018-t01); FORGED part: Air-Way NON-forged row FF6804-8-6-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>Air-Way FF6804 (s38, double-pass 2026-10-15, parts.air-way.com/api/series/38, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p18 FS6804-10-10-10-NWO-FG (ORFS-p018-t01); FORGED part: Air-Way NON-forged row FF6804-10-10-10 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6804 (s38, double-pass 2026-10-15, parts.air-way.com/api/series/38, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p18 FS6804-10-10-10-NWO-FG (ORFS-p018-t01); FORGED part: Air-Way NON-forged row FF6804-10-10-10 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
